--- a/Wave/width_and_speed_combined.xlsx
+++ b/Wave/width_and_speed_combined.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weizhechen/Documents/Champerlab/DSXmegaTOXIN/Modeling/Github/Wave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DD00B2-733B-E64F-8165-4A59EE1C3745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7BE4F1-FAFE-854C-9529-462779847104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="1320" windowWidth="19540" windowHeight="16960" xr2:uid="{2059E8D1-C0B2-3248-A10B-3C567D23FF9D}"/>
+    <workbookView xWindow="600" yWindow="740" windowWidth="19540" windowHeight="16880" xr2:uid="{2059E8D1-C0B2-3248-A10B-3C567D23FF9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>homing_dom</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,14 +54,6 @@
   </si>
   <si>
     <t>TADE suppression</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -179,11 +171,38 @@
     <t>TADFI modification (DR05)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">SEM of average_width </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEM of average_speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD of average_gens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD of average_width (fraction)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEM of average_width (fraction)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEM of average_gens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="12"/>
@@ -247,7 +266,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -266,7 +285,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,12 +608,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F9C7CA-2364-FF4F-827E-95DD34BDEA6C}">
-  <dimension ref="A2:K17"/>
+  <dimension ref="A2:K18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="28" style="4" customWidth="1"/>
     <col min="5" max="5" width="15" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="4" customWidth="1"/>
@@ -598,39 +623,46 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <f>31.33*D3</f>
         <v>9.3238079999999979</v>
       </c>
-      <c r="D3" s="3">
+      <c r="C3" s="6">
+        <f>H3*31.33</f>
+        <v>7.0229954600000005E-2</v>
+      </c>
+      <c r="D3" s="8">
         <v>0.29759999999999998</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="8">
         <v>3.4700000000000002E-2</v>
       </c>
       <c r="F3" s="3">
@@ -639,28 +671,32 @@
       <c r="G3" s="3">
         <v>239</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="8">
         <v>2.2416200000000002E-3</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <f t="shared" ref="B4:B5" si="0">31.33*D4</f>
         <v>17.112445999999998</v>
       </c>
-      <c r="D4" s="3">
+      <c r="C4" s="6">
+        <f t="shared" ref="C4:C9" si="1">H4*31.33</f>
+        <v>0.34729869959511189</v>
+      </c>
+      <c r="D4" s="8">
         <v>0.54620000000000002</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="8">
         <v>0.15079999999999999</v>
       </c>
       <c r="F4" s="3">
@@ -669,25 +705,29 @@
       <c r="G4" s="3">
         <v>185</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="8">
         <v>1.108518032541053E-2</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <f t="shared" si="0"/>
         <v>12.080848</v>
       </c>
-      <c r="D5" s="3">
+      <c r="C5" s="6">
+        <f t="shared" si="1"/>
+        <v>0.28739064440222489</v>
+      </c>
+      <c r="D5" s="8">
         <v>0.3856</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="8">
         <v>0.13700000000000001</v>
       </c>
       <c r="F5" s="3">
@@ -696,25 +736,29 @@
       <c r="G5" s="3">
         <v>223</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="8">
         <v>9.1730176955705373E-3</v>
       </c>
       <c r="K5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="5">
+        <v>26</v>
+      </c>
+      <c r="B6" s="6">
         <f>31.33*D6</f>
         <v>23.394110999999999</v>
       </c>
-      <c r="D6" s="3">
+      <c r="C6" s="6">
+        <f t="shared" si="1"/>
+        <v>0.14095367</v>
+      </c>
+      <c r="D6" s="8">
         <v>0.74670000000000003</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="8">
         <v>7.1690000000000004E-2</v>
       </c>
       <c r="F6" s="3">
@@ -723,25 +767,29 @@
       <c r="G6" s="3">
         <v>254</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="8">
         <v>4.4990000000000004E-3</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
         <f>31.33*D7*2</f>
         <v>25.082797999999997</v>
       </c>
-      <c r="D7" s="3">
+      <c r="C7" s="6">
+        <f t="shared" si="1"/>
+        <v>6.3537239999999995E-2</v>
+      </c>
+      <c r="D7" s="8">
         <v>0.40029999999999999</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="8">
         <v>8.1392000000000006E-2</v>
       </c>
       <c r="F7" s="3">
@@ -750,7 +798,7 @@
       <c r="G7" s="3">
         <v>1611</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="8">
         <v>2.0279999999999999E-3</v>
       </c>
     </row>
@@ -758,14 +806,18 @@
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5">
-        <f t="shared" ref="B8:B9" si="1">31.33*D8</f>
+      <c r="B8" s="6">
+        <f t="shared" ref="B8:B9" si="2">31.33*D8</f>
         <v>11.87407</v>
       </c>
-      <c r="D8" s="3">
+      <c r="C8" s="6">
+        <f t="shared" si="1"/>
+        <v>5.0346056799999997E-2</v>
+      </c>
+      <c r="D8" s="8">
         <v>0.379</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="8">
         <v>4.896665E-2</v>
       </c>
       <c r="F8" s="3">
@@ -774,28 +826,32 @@
       <c r="G8" s="3">
         <v>927</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="8">
         <v>1.6069599999999999E-3</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6">
+        <f t="shared" si="2"/>
+        <v>6.3197257689967898</v>
+      </c>
+      <c r="C9" s="6">
         <f t="shared" si="1"/>
-        <v>6.3197257689967898</v>
-      </c>
-      <c r="D9" s="3">
+        <v>4.6001156583542783E-3</v>
+      </c>
+      <c r="D9" s="8">
         <v>0.20171483463124132</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="8">
         <v>6.8601754664496398E-3</v>
       </c>
       <c r="F9" s="3">
@@ -804,184 +860,216 @@
       <c r="G9" s="3">
         <v>2183</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="8">
         <v>1.4682782184341776E-4</v>
       </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="5"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="6"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="B11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="5">
-        <f>15.67/D12</f>
-        <v>1.2779834671485069</v>
-      </c>
-      <c r="D12" s="4">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6">
+        <f>31.33/(2*D12)</f>
+        <v>1.2775756868462895</v>
+      </c>
+      <c r="C12" s="6">
+        <f>31.33*G12/(2*D12*D12)</f>
+        <v>7.8492521999856558E-3</v>
+      </c>
+      <c r="D12" s="6">
         <v>12.261504473890884</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="8">
         <v>0.33689952903712395</v>
       </c>
       <c r="F12" s="3">
         <v>20</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="8">
         <v>7.533302485146734E-2</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5">
-        <f t="shared" ref="B13:B17" si="2">15.67/D13</f>
-        <v>1.2809064180321095</v>
-      </c>
-      <c r="D13" s="4">
+        <v>24</v>
+      </c>
+      <c r="B13" s="6">
+        <f t="shared" ref="B13:B18" si="3">31.33/(2*D13)</f>
+        <v>1.280497705071665</v>
+      </c>
+      <c r="C13" s="6">
+        <f t="shared" ref="C13:C17" si="4">31.33*G13/(2*D13*D13)</f>
+        <v>1.6054693755026297E-2</v>
+      </c>
+      <c r="D13" s="6">
         <v>12.233524463148711</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="8">
         <v>0.68594581993000392</v>
       </c>
       <c r="F13" s="3">
         <v>20</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="8">
         <v>0.15338214822453186</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="5">
-        <f t="shared" si="2"/>
-        <v>1.2681925570635286</v>
-      </c>
-      <c r="D14" s="4">
+        <v>23</v>
+      </c>
+      <c r="B14" s="6">
+        <f t="shared" si="3"/>
+        <v>1.2677879008551483</v>
+      </c>
+      <c r="C14" s="6">
+        <f t="shared" si="4"/>
+        <v>7.1869556230940053E-3</v>
+      </c>
+      <c r="D14" s="6">
         <v>12.356167770203236</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="8">
         <v>0.31325438191414556</v>
       </c>
       <c r="F14" s="3">
         <v>20</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="8">
         <v>7.004580922097102E-2</v>
       </c>
       <c r="J14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="5">
-        <f t="shared" si="2"/>
-        <v>0.15651138966316844</v>
-      </c>
-      <c r="D15" s="4">
+        <v>29</v>
+      </c>
+      <c r="B15" s="6">
+        <f t="shared" si="3"/>
+        <v>0.15646144984515209</v>
+      </c>
+      <c r="C15" s="6">
+        <f t="shared" si="4"/>
+        <v>2.2049317524780931E-3</v>
+      </c>
+      <c r="D15" s="6">
         <v>100.12050901677985</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="8">
         <v>10.929152235779613</v>
       </c>
       <c r="F15" s="3">
         <v>60</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="8">
         <v>1.4109474865779998</v>
       </c>
       <c r="J15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="5">
-        <f t="shared" si="2"/>
-        <v>0.27236935166790915</v>
-      </c>
-      <c r="D16" s="4">
+        <v>22</v>
+      </c>
+      <c r="B16" s="6">
+        <f t="shared" si="3"/>
+        <v>0.27228244377012101</v>
+      </c>
+      <c r="C16" s="6">
+        <f t="shared" si="4"/>
+        <v>8.8553916912301883E-3</v>
+      </c>
+      <c r="D16" s="6">
         <v>57.53217057661432</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="8">
         <v>8.3678501263104916</v>
       </c>
       <c r="F16" s="3">
         <v>20</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="8">
         <v>1.871108170796046</v>
       </c>
       <c r="J16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="5">
-        <f>15.67/D17</f>
-        <v>0.4006272258335557</v>
-      </c>
-      <c r="D17" s="4">
+        <v>30</v>
+      </c>
+      <c r="B17" s="6">
+        <f t="shared" si="3"/>
+        <v>0.40049939327904593</v>
+      </c>
+      <c r="C17" s="6">
+        <f t="shared" si="4"/>
+        <v>1.0991020935273948E-3</v>
+      </c>
+      <c r="D17" s="6">
         <v>39.113667243649203</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="6">
         <v>0.54733268457620221</v>
       </c>
       <c r="F17" s="4">
         <v>26</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="6">
         <v>0.10734077073389153</v>
       </c>
       <c r="J17" t="s">
-        <v>11</v>
-      </c>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="B18" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
